--- a/output/pdf_financials_xlsx/FOXT.xlsx
+++ b/output/pdf_financials_xlsx/FOXT.xlsx
@@ -6217,10 +6217,10 @@
         <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.52015</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>4.671382</v>
       </c>
     </row>
     <row r="93">
@@ -7726,25 +7726,25 @@
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>0.03178</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>0.019389</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>0.010762</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.05034</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>0.010308</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0</v>
@@ -10594,7 +10594,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -32006,7 +32010,11 @@
           <t>Accounts payable related to exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FOXT.xlsx
+++ b/output/pdf_financials_xlsx/FOXT.xlsx
@@ -1065,43 +1065,43 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003251</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.014513</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006998</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001052</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.014018</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.004032</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.007681</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.008288</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001414</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.002844</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.003099</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2088,43 +2088,43 @@
         <v>-0.088697</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.980886</v>
+        <v>-0.984137</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.8267910000000001</v>
+        <v>-0.8413040000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.591831</v>
+        <v>-0.610831</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.533007</v>
+        <v>-0.540005</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.539991</v>
+        <v>-0.5410430000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.407239</v>
+        <v>-0.421257</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.59331</v>
+        <v>-0.597342</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.528264</v>
+        <v>-0.535945</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.522688</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.585798</v>
+        <v>-0.594086</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.397866</v>
+        <v>-0.39928</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.700234</v>
+        <v>-0.703078</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.417356</v>
+        <v>-0.420455</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.83525</v>
@@ -2210,43 +2210,43 @@
         <v>-0.088697</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.980886</v>
+        <v>-0.984137</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.8267910000000001</v>
+        <v>-0.8413040000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.591831</v>
+        <v>-0.610831</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.531377</v>
+        <v>-0.538375</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.533739</v>
+        <v>-0.534791</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.400987</v>
+        <v>-0.415005</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.589546</v>
+        <v>-0.5935780000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.525759</v>
+        <v>-0.53344</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.5203759999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.585798</v>
+        <v>-0.594086</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.397866</v>
+        <v>-0.39928</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.700234</v>
+        <v>-0.703078</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.417356</v>
+        <v>-0.420455</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.83525</v>
@@ -9740,7 +9740,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -11912,7 +11916,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13450,7 +13458,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -15638,7 +15650,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -19628,7 +19644,11 @@
           <t>Reclamation deposit 7 52,500</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -21942,7 +21962,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>0.0435</v>
       </c>
@@ -27110,7 +27134,11 @@
           <t>Increase (decrease) in reclamation deposits</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -29854,7 +29882,11 @@
           <t>(Increase) decrease in reclamation deposits</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -31308,7 +31340,11 @@
           <t>Increase in reclamation deposits</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -33938,7 +33974,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -36934,7 +36974,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -38612,7 +38656,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E292" s="5" t="n">
         <v>-0.0025</v>
       </c>
@@ -49690,7 +49738,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">

--- a/output/pdf_financials_xlsx/FOXT.xlsx
+++ b/output/pdf_financials_xlsx/FOXT.xlsx
@@ -2176,16 +2176,16 @@
         <v>0.002312</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.015433</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.015433</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.015432</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.012861</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -2237,16 +2237,16 @@
         <v>-0.5203759999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.594086</v>
+        <v>-0.578653</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.39928</v>
+        <v>-0.383847</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.703078</v>
+        <v>-0.687646</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.420455</v>
+        <v>-0.407594</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.83525</v>
@@ -6640,16 +6640,16 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.015433</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.015433</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.015432</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.012861</v>
       </c>
       <c r="Q100" s="3" t="n">
         <v>0</v>
@@ -7872,10 +7872,10 @@
         <v>0</v>
       </c>
       <c r="Q120" s="3" t="n">
-        <v>0</v>
+        <v>0.628511</v>
       </c>
       <c r="R120" s="3" t="n">
-        <v>0</v>
+        <v>0.4853</v>
       </c>
       <c r="S120" s="3" t="n">
         <v>0</v>
@@ -29610,7 +29610,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -30818,7 +30822,11 @@
           <t>Depreciation - right-of-use asset</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -31652,7 +31660,11 @@
           <t>Depreciation – right-of-use asset</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FOXT.xlsx
+++ b/output/pdf_financials_xlsx/FOXT.xlsx
@@ -1370,31 +1370,31 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.294854</v>
+        <v>-0.294854</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.109781</v>
+        <v>-0.109781</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.433595</v>
+        <v>-0.433595</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.385191</v>
+        <v>0.385191</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.121681</v>
+        <v>-0.121681</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.085594</v>
+        <v>-0.085684</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.025966</v>
+        <v>-0.025966</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.31009</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.120457</v>
+        <v>-0.120457</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.036431</v>
@@ -2383,7 +2383,7 @@
         <v>-22.53389408341991</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-21.01812449200592</v>
+        <v>-21.04022453645157</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-4.376464242975847</v>
@@ -4587,55 +4587,55 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02816</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.02618</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.031371</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.148036</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.0775</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="68">
@@ -4654,49 +4654,49 @@
         <v>0.049282</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.034005</v>
+        <v>0.050005</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.06839199999999999</v>
+        <v>0.09839199999999999</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.126574</v>
+        <v>0.156574</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.049703</v>
+        <v>0.072203</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.064446</v>
+        <v>0.09260599999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.033151</v>
+        <v>0.050251</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.040857</v>
+        <v>0.057857</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.039693</v>
+        <v>0.060693</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.028809</v>
+        <v>0.046809</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.100867</v>
+        <v>0.127047</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.038362</v>
+        <v>0.069733</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.278692</v>
+        <v>0.426728</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.183843</v>
+        <v>0.261343</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0.120715</v>
+        <v>0.140715</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.127576</v>
+        <v>0.152576</v>
       </c>
     </row>
     <row r="69">
@@ -5099,22 +5099,22 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.009634999999999999</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.037819</v>
+        <v>0.016819</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.114727</v>
+        <v>0.09672699999999999</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.123378</v>
+        <v>0.09719800000000001</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.03258</v>
+        <v>0.001209</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.001322</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
         <v>0</v>
@@ -7265,10 +7265,10 @@
         <v>0</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>-0.141171</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>-0.445638</v>
       </c>
     </row>
     <row r="111">
@@ -7281,25 +7281,25 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001834</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023965</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001921</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01926</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -7564,10 +7564,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.007003</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -8726,25 +8726,25 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001834</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023965</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001921</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01926</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -8797,10 +8797,10 @@
         <v>-0.728814</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.46088</v>
+        <v>-0.484845</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.383869</v>
+        <v>-0.386869</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>-0.5023570000000001</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.343559</v>
+        <v>-0.362819</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.4444</v>
@@ -25956,7 +25956,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -26380,7 +26384,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -27456,7 +27464,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -28378,7 +28390,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28872,7 +28888,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -29994,7 +30014,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -31454,7 +31478,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -32350,7 +32378,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -32866,7 +32898,11 @@
           <t>Deferred income tax (recovery) loss</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33370,7 +33406,11 @@
           <t>Deferred income tax loss (recovery)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -33686,7 +33726,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -33886,7 +33930,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -35316,7 +35364,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -37414,7 +37466,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -38252,7 +38308,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -43250,7 +43310,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
         <v>-0.059782</v>
       </c>
@@ -52216,7 +52280,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -53696,7 +53764,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -55228,7 +55300,11 @@
           <t>Deferred income tax recovery (expense) 11</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
